--- a/0_exampleData/Findings.xlsx
+++ b/0_exampleData/Findings.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CRM\Table2KnowledgeModeller\ExampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CRM\Ausbau_GraphExplorer\OntoCartographer-Studio\0_exampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD5C619-B4CE-4619-BD7C-250AD57E7050}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBC16B00-A0EF-4B81-9F3F-F449A65DEAE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="15238" xr2:uid="{94155C5D-A99C-44BF-B306-4250CEDD9F75}"/>
+    <workbookView xWindow="2160" yWindow="2385" windowWidth="21600" windowHeight="11235" xr2:uid="{94155C5D-A99C-44BF-B306-4250CEDD9F75}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="63">
   <si>
     <t>Material_ID</t>
   </si>
@@ -45,12 +45,6 @@
     <t>Material</t>
   </si>
   <si>
-    <t>Fundnummer</t>
-  </si>
-  <si>
-    <t>ID_Schicht</t>
-  </si>
-  <si>
     <t>ID_Embedding</t>
   </si>
   <si>
@@ -211,6 +205,27 @@
   </si>
   <si>
     <t>Geometry</t>
+  </si>
+  <si>
+    <t>ID_StratigraphicalUnit</t>
+  </si>
+  <si>
+    <t>Inventorynumber</t>
+  </si>
+  <si>
+    <t>Art_DE</t>
+  </si>
+  <si>
+    <t>Peitsche, fragmentiert</t>
+  </si>
+  <si>
+    <t>Ostrake, mit antiker Karte</t>
+  </si>
+  <si>
+    <t>Amulett, mit geometrischem Dekor</t>
+  </si>
+  <si>
+    <t>Statuette, antropomorph</t>
   </si>
 </sst>
 </file>
@@ -562,34 +577,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FF13478-00D0-4F99-BDEE-0661BBBF5259}">
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.05" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="38.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="50.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.140625" customWidth="1"/>
+    <col min="8" max="9" width="32.28515625" customWidth="1"/>
+    <col min="10" max="10" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="50.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="B1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -598,174 +613,189 @@
         <v>1</v>
       </c>
       <c r="G1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="H1" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" t="s">
         <v>52</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" t="s">
         <v>54</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>55</v>
       </c>
-      <c r="K1" t="s">
-        <v>56</v>
-      </c>
-      <c r="L1" t="s">
-        <v>57</v>
-      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
         <v>33</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J2" t="s">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J3" t="s">
+        <v>42</v>
+      </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
         <v>35</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C4" t="s">
         <v>39</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D4" t="s">
         <v>5</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E4" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G4" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H4" t="s">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I4" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" t="s">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K4" t="s">
         <v>25</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L4" t="s">
         <v>47</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" t="s">
         <v>36</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C5" t="s">
         <v>40</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G5" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H5" t="s">
         <v>22</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" t="s">
         <v>44</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K5" t="s">
         <v>26</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L5" t="s">
         <v>48</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M5" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" t="s">
-        <v>45</v>
-      </c>
-      <c r="J4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" t="s">
-        <v>49</v>
-      </c>
-      <c r="L4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K5" t="s">
-        <v>50</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
       </c>
     </row>
   </sheetData>
